--- a/Result/profitability/5604.xlsx
+++ b/Result/profitability/5604.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4425</v>
+        <v>0.2475</v>
       </c>
       <c r="N2" t="n">
-        <v>75.7075</v>
+        <v>75.64875000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.43</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2625</v>
+        <v>0.275</v>
       </c>
       <c r="N3" t="n">
-        <v>69.63</v>
+        <v>70.015</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.37</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2825</v>
+        <v>0.29375</v>
       </c>
       <c r="N4" t="n">
-        <v>63.86625</v>
+        <v>63.9075</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>0.32875</v>
+        <v>0.34125</v>
       </c>
       <c r="N5" t="n">
-        <v>58.58875</v>
+        <v>58.73875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3075</v>
+        <v>0.32125</v>
       </c>
       <c r="N6" t="n">
-        <v>51.78125</v>
+        <v>52.07624999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0.32625</v>
+        <v>0.33875</v>
       </c>
       <c r="N7" t="n">
-        <v>46.06999999999999</v>
+        <v>46.1425</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>0.355</v>
+        <v>0.35375</v>
       </c>
       <c r="N8" t="n">
-        <v>40.41499999999999</v>
+        <v>40.435</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5604</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>41</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7</v>
+      </c>
+      <c r="E75" t="n">
+        <v>34</v>
+      </c>
+      <c r="F75" t="n">
+        <v>83.06</v>
+      </c>
+      <c r="G75" t="n">
+        <v>29</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>69.73%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>40</v>
+      </c>
+      <c r="K75" t="n">
+        <v>34</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.44375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>82.155</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.03125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.1599999999999966</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.001930036188178441</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4761904761904763</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.200000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01465917419985341</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
